--- a/Preferences/preferences.xlsx
+++ b/Preferences/preferences.xlsx
@@ -4729,7 +4729,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D67" t="n">
         <v>69</v>
